--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_258_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_258_R26.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9223</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9891</v>
+        <v>4.4176</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9332</v>
+        <v>4.0004</v>
       </c>
       <c r="G2" t="n">
         <v>6.5062</v>
@@ -610,13 +610,13 @@
         <v>3.7112</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1896</v>
+        <v>-0.6939</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.4439</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3172</v>
+        <v>-0.25</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.354</v>
+        <v>5.8737</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7394</v>
+        <v>6.1247</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3855</v>
+        <v>-0.251</v>
       </c>
       <c r="G3" t="n">
         <v>6.6432</v>
@@ -688,13 +688,13 @@
         <v>3.7112</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6087</v>
+        <v>-1.089</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1791</v>
+        <v>-0.7938</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4296</v>
+        <v>-0.2952</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1946</v>
+        <v>3.0518</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0343</v>
+        <v>0.3942</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2289</v>
+        <v>2.6576</v>
       </c>
       <c r="G4" t="n">
         <v>0.979</v>
@@ -766,13 +766,13 @@
         <v>3.7112</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9827</v>
+        <v>-1.1255</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2617</v>
+        <v>-0.8331</v>
       </c>
       <c r="U4" t="n">
-        <v>0.279</v>
+        <v>-0.2923</v>
       </c>
       <c r="V4" t="n">
         <v>0.6468</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4446</v>
+        <v>0.0105</v>
       </c>
       <c r="E5" t="n">
-        <v>3.132</v>
+        <v>1.866</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6875</v>
+        <v>-1.8555</v>
       </c>
       <c r="G5" t="n">
         <v>0.2112</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2876</v>
+        <v>-0.1465</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6201</v>
+        <v>0.3541</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3325</v>
+        <v>-0.5006</v>
       </c>
       <c r="V5" t="n">
         <v>-1.214</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1815</v>
+        <v>-0.1143</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0579</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1236</v>
+        <v>-0.0564</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2263</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1871</v>
+        <v>-0.1199</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.537</v>
+        <v>-0.4698</v>
       </c>
       <c r="E8" t="n">
         <v>-1.5534</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0163</v>
+        <v>1.0835</v>
       </c>
       <c r="G8" t="n">
         <v>0.3331</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4938</v>
+        <v>-0.4266</v>
       </c>
       <c r="T8" t="n">
         <v>-0.5149</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0211</v>
+        <v>0.0883</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7169</v>
+        <v>-1.5488</v>
       </c>
       <c r="E9" t="n">
         <v>-1.7642</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0473</v>
+        <v>0.2154</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4476</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5012</v>
+        <v>-0.3332</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1752</v>
+        <v>-1.9564</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4101</v>
+        <v>-2.2921</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2349</v>
+        <v>0.3357</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8611</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5461</v>
+        <v>-0.3273</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4046</v>
+        <v>-0.3038</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7558</v>
+        <v>-2.6064</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6982</v>
+        <v>-1.5489</v>
       </c>
       <c r="F11" t="n">
         <v>-1.0576</v>
@@ -1312,10 +1312,10 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2344</v>
+        <v>-1.0851</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6642</v>
+        <v>-0.5149</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5702</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.376</v>
+        <v>-3.0794</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1399</v>
+        <v>-2.7566</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2361</v>
+        <v>-0.3228</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7512</v>
+        <v>-3.2333</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6675</v>
+        <v>-2.0588</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0837</v>
+        <v>-1.1745</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6973</v>
+        <v>-2.2252</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9845</v>
+        <v>-0.7962</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7127</v>
+        <v>-1.429</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0539</v>
+        <v>-1.0081</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-1.2626</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6291</v>
+        <v>0.2545</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1598</v>
+        <v>3.0154</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5526</v>
+        <v>-1.1657</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2829</v>
+        <v>-0.4439</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2697</v>
+        <v>-0.7218</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6499</v>
+        <v>-3.3088</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2599</v>
+        <v>-3.1399</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.39</v>
+        <v>-0.1689</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.2333</v>
+        <v>-1.7512</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0588</v>
+        <v>-1.6675</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1745</v>
+        <v>-0.0837</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2252</v>
+        <v>-1.6973</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7962</v>
+        <v>-0.9845</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.429</v>
+        <v>-0.7127</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0081</v>
+        <v>-0.0539</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2626</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2545</v>
+        <v>0.6291</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>3.0154</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7361</v>
+        <v>-0.4854</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.2829</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.789</v>
+        <v>-0.2025</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.435899999999997</v>
+        <v>4.182799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.040599999999999</v>
+        <v>-0.2936999999999963</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4762</v>
+        <v>4.4763</v>
       </c>
       <c r="G14" t="n">
         <v>5.7738</v>
@@ -1531,7 +1531,7 @@
         <v>-6.523599999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.0474</v>
+        <v>-8.047400000000001</v>
       </c>
       <c r="O14" t="n">
         <v>1.5237</v>
@@ -1546,13 +1546,13 @@
         <v>20.8759</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.7447</v>
+        <v>-6.9981</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6172</v>
+        <v>-3.8702</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.1277</v>
+        <v>-3.1278</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7116</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3726</v>
+        <v>5.4626</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3303</v>
+        <v>4.9148</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0423</v>
+        <v>0.5477</v>
       </c>
       <c r="G15" t="n">
         <v>2.3599</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9764</v>
+        <v>1.0664</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7616</v>
+        <v>0.3462</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2148</v>
+        <v>0.7202</v>
       </c>
       <c r="V15" t="n">
         <v>2.9641</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9379</v>
+        <v>3.0051</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4051</v>
+        <v>1.3487</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5328</v>
+        <v>1.6564</v>
       </c>
       <c r="G16" t="n">
         <v>1.1434</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0444</v>
+        <v>1.1116</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8883</v>
+        <v>0.0553</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9326</v>
+        <v>1.0563</v>
       </c>
       <c r="V16" t="n">
         <v>1.214</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1126</v>
+        <v>1.0139</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9825</v>
+        <v>2.6192</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0951</v>
+        <v>-1.6054</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3739</v>
+        <v>-1.1539</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4861</v>
+        <v>-0.7622</v>
       </c>
       <c r="I17" t="n">
-        <v>0.86</v>
+        <v>-0.3917</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3643</v>
+        <v>1.3738</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5546</v>
+        <v>1.9697</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8097</v>
+        <v>-0.5959</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-2.5277</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0406</v>
+        <v>-2.7319</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0502</v>
+        <v>0.2042</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>2.432</v>
+        <v>1.3122</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1325</v>
+        <v>0.4052</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2995</v>
+        <v>0.9069</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9524</v>
+        <v>0.3854</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9731</v>
+        <v>-0.8179</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0207</v>
+        <v>1.2033</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1539</v>
+        <v>-0.7795</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7622</v>
+        <v>-0.1405</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3917</v>
+        <v>-0.639</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3738</v>
+        <v>-0.036</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9697</v>
+        <v>0.1246</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5959</v>
+        <v>-0.1607</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5277</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.7319</v>
+        <v>-0.2651</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2042</v>
+        <v>-0.4783</v>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.3917</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.6237</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.2507</v>
+        <v>1.0231</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7591</v>
+        <v>0.4681</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4916</v>
+        <v>0.5551</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4926</v>
+        <v>0.2375</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2281</v>
+        <v>-1.4543</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7208</v>
+        <v>1.6918</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7795</v>
+        <v>0.3739</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1405</v>
+        <v>-0.4861</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.639</v>
+        <v>0.86</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.036</v>
+        <v>1.3643</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1246</v>
+        <v>0.5546</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1607</v>
+        <v>0.8097</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2651</v>
+        <v>-1.0406</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4783</v>
+        <v>0.0502</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1303</v>
+        <v>1.5569</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0578</v>
+        <v>0.6607</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0725</v>
+        <v>0.8962</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4346</v>
+        <v>-0.8086</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4889</v>
+        <v>0.1258</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0543</v>
+        <v>-0.9344</v>
       </c>
       <c r="G20" t="n">
-        <v>1.235</v>
+        <v>-1.9167</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4357</v>
+        <v>-0.3241</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2007</v>
+        <v>-1.5927</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8997</v>
+        <v>-1.5023</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3108</v>
+        <v>-0.7527</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5889</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6647</v>
+        <v>-0.4144</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1249</v>
+        <v>0.4287</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7896</v>
+        <v>-0.8431</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2788</v>
+        <v>0.34</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7196</v>
+        <v>0.0198</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5592</v>
+        <v>0.3203</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3247</v>
+        <v>0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7886</v>
+        <v>1.6083</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1346</v>
+        <v>-0.9895</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1101</v>
+        <v>0.3615</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0245</v>
+        <v>-1.351</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9167</v>
+        <v>-0.2898</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3241</v>
+        <v>-0.7382</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5927</v>
+        <v>0.4483</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5023</v>
+        <v>1.4582</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7527</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.8196</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4144</v>
+        <v>-1.7481</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4287</v>
+        <v>-1.3767</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8431</v>
+        <v>-0.3713</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0141</v>
+        <v>0.6045</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2161</v>
+        <v>0.063</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2302</v>
+        <v>0.5414</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8931</v>
+        <v>-1.1581</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0077</v>
+        <v>-0.8428</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9008</v>
+        <v>-0.3154</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2898</v>
+        <v>1.235</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7382</v>
+        <v>1.4357</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4483</v>
+        <v>-0.2007</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4582</v>
+        <v>1.8997</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6385999999999999</v>
+        <v>1.3108</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8196</v>
+        <v>0.5889</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7481</v>
+        <v>-0.6647</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3767</v>
+        <v>0.1249</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3713</v>
+        <v>-0.7896</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2992</v>
+        <v>0.5553</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2908</v>
+        <v>0.3657</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0083</v>
+        <v>0.1896</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-1.3247</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9296</v>
+        <v>-1.7393</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.157</v>
+        <v>-1.4493</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7726</v>
+        <v>-0.29</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9565</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0452</v>
+        <v>1.145</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3655</v>
+        <v>0.3422</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3203</v>
+        <v>0.8028</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8877</v>
+        <v>-3.0063</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3815</v>
+        <v>-3.7918</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4938</v>
+        <v>0.7855</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5085</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5236</v>
+        <v>0.3578</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5149</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.2829</v>
       </c>
       <c r="V24" t="n">
         <v>0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0242</v>
+        <v>-3.4795</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3082</v>
+        <v>-4.9543</v>
       </c>
       <c r="F25" t="n">
-        <v>1.284</v>
+        <v>1.4748</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2812</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4863</v>
+        <v>1.031</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0272</v>
+        <v>0.3266</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5135</v>
+        <v>0.7044</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1418</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.4357</v>
+        <v>-1.076799999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.940099999999999</v>
+        <v>-3.9404</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5044999999999999</v>
+        <v>2.8633</v>
       </c>
       <c r="G26" t="n">
         <v>-5.773899999999999</v>
@@ -2455,7 +2455,7 @@
         <v>-3.9318</v>
       </c>
       <c r="J26" t="n">
-        <v>6.523700000000001</v>
+        <v>6.523699999999999</v>
       </c>
       <c r="K26" t="n">
         <v>8.0474</v>
@@ -2467,7 +2467,7 @@
         <v>-12.2976</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.889500000000002</v>
+        <v>-9.8895</v>
       </c>
       <c r="O26" t="n">
         <v>-2.4081</v>
@@ -2482,13 +2482,13 @@
         <v>12.7575</v>
       </c>
       <c r="S26" t="n">
-        <v>7.745</v>
+        <v>10.1038</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1278</v>
+        <v>3.1277</v>
       </c>
       <c r="U26" t="n">
-        <v>4.6171</v>
+        <v>6.976099999999999</v>
       </c>
       <c r="V26" t="n">
         <v>2.711600000000001</v>
